--- a/artfynd/A 32045-2020 artfynd.xlsx
+++ b/artfynd/A 32045-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32045-2020 artfynd.xlsx
+++ b/artfynd/A 32045-2020 artfynd.xlsx
@@ -5910,7 +5910,7 @@
         <v>94487074</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>94526736</v>
       </c>
       <c r="B48" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>94486575</v>
       </c>
       <c r="B52" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>94492384</v>
       </c>
       <c r="B144" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>

--- a/artfynd/A 32045-2020 artfynd.xlsx
+++ b/artfynd/A 32045-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY159"/>
+  <dimension ref="A1:AY157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>91953603</v>
+        <v>91953599</v>
       </c>
       <c r="B24" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,25 +3249,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464269.8333737765</v>
+        <v>464400.113392368</v>
       </c>
       <c r="R24" t="n">
-        <v>7106524.855028595</v>
+        <v>7106577.176908364</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91953599</v>
+        <v>91953601</v>
       </c>
       <c r="B25" t="n">
         <v>78596</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464400.113392368</v>
+        <v>464269.8333737765</v>
       </c>
       <c r="R25" t="n">
-        <v>7106577.176908364</v>
+        <v>7106524.855028595</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>91953601</v>
+        <v>91953612</v>
       </c>
       <c r="B26" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464269.8333737765</v>
+        <v>464218.8627969068</v>
       </c>
       <c r="R26" t="n">
-        <v>7106524.855028595</v>
+        <v>7106473.810835057</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>91953612</v>
+        <v>91953600</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
+        <v>78602</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3597,25 +3597,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464218.8627969068</v>
+        <v>464400.113392368</v>
       </c>
       <c r="R27" t="n">
-        <v>7106473.810835057</v>
+        <v>7106577.176908364</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>91953600</v>
+        <v>91953611</v>
       </c>
       <c r="B28" t="n">
-        <v>78602</v>
+        <v>78570</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3713,25 +3713,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464400.113392368</v>
+        <v>464218.8627969068</v>
       </c>
       <c r="R28" t="n">
-        <v>7106577.176908364</v>
+        <v>7106473.810835057</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>91953611</v>
+        <v>91953609</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
+        <v>78602</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,25 +3829,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91953609</v>
+        <v>91953610</v>
       </c>
       <c r="B30" t="n">
-        <v>78602</v>
+        <v>78596</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4049,10 +4049,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91953610</v>
+        <v>91847660</v>
       </c>
       <c r="B31" t="n">
-        <v>78596</v>
+        <v>73686</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4061,25 +4061,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4089,13 +4089,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464218.8627969068</v>
+        <v>463995.1497236547</v>
       </c>
       <c r="R31" t="n">
-        <v>7106473.810835057</v>
+        <v>7105315.786187577</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>91847660</v>
+        <v>91847667</v>
       </c>
       <c r="B32" t="n">
-        <v>73686</v>
+        <v>85703</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463995.1497236547</v>
+        <v>463022.0433624045</v>
       </c>
       <c r="R32" t="n">
-        <v>7105315.786187577</v>
+        <v>7105268.995182605</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4259,6 +4259,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4281,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>91847667</v>
+        <v>91847635</v>
       </c>
       <c r="B33" t="n">
-        <v>85703</v>
+        <v>73678</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4293,25 +4294,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4321,10 +4322,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463022.0433624045</v>
+        <v>462919.7975275204</v>
       </c>
       <c r="R33" t="n">
-        <v>7105268.995182605</v>
+        <v>7105479.002424857</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4375,7 +4376,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>91847635</v>
+        <v>91847636</v>
       </c>
       <c r="B34" t="n">
-        <v>73678</v>
+        <v>73698</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4410,25 +4410,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91847636</v>
+        <v>91953584</v>
       </c>
       <c r="B35" t="n">
-        <v>73698</v>
+        <v>85703</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4530,21 +4530,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462919.7975275204</v>
+        <v>463012.0474326991</v>
       </c>
       <c r="R35" t="n">
-        <v>7105479.002424857</v>
+        <v>7105276.117761587</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4608,6 +4608,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4630,10 +4631,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>91953584</v>
+        <v>91847653</v>
       </c>
       <c r="B36" t="n">
-        <v>85703</v>
+        <v>78570</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4646,21 +4647,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4670,13 +4671,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463012.0474326991</v>
+        <v>462649.8813285625</v>
       </c>
       <c r="R36" t="n">
-        <v>7105276.117761587</v>
+        <v>7105045.818662897</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4724,7 +4725,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91847653</v>
+        <v>91847668</v>
       </c>
       <c r="B37" t="n">
         <v>78570</v>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462649.8813285625</v>
+        <v>463022.927398206</v>
       </c>
       <c r="R37" t="n">
-        <v>7105045.818662897</v>
+        <v>7104938.045288703</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91847668</v>
+        <v>91847638</v>
       </c>
       <c r="B38" t="n">
         <v>78570</v>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463022.927398206</v>
+        <v>462960.9582429578</v>
       </c>
       <c r="R38" t="n">
-        <v>7104938.045288703</v>
+        <v>7104961.109504571</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91847638</v>
+        <v>94487170</v>
       </c>
       <c r="B39" t="n">
-        <v>78570</v>
+        <v>89952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4991,38 +4991,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462960.9582429578</v>
+        <v>462836.8511866148</v>
       </c>
       <c r="R39" t="n">
-        <v>7104961.109504571</v>
+        <v>7104736.255084063</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5049,7 +5050,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5059,12 +5060,17 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stark doft av doftticka intill en sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5084,21 +5090,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>94487170</v>
+        <v>94487503</v>
       </c>
       <c r="B40" t="n">
-        <v>89952</v>
+        <v>78570</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5107,25 +5109,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5136,10 +5138,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462836.8511866148</v>
+        <v>462970.2618030491</v>
       </c>
       <c r="R40" t="n">
-        <v>7104736.255084063</v>
+        <v>7104858.996409122</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5182,11 +5184,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Stark doft av doftticka intill en sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5213,10 +5210,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>94487503</v>
+        <v>94487080</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
+        <v>95519</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,39 +5222,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462970.2618030491</v>
+        <v>462828.0327530226</v>
       </c>
       <c r="R41" t="n">
-        <v>7104858.996409122</v>
+        <v>7104731.982492823</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5326,10 +5324,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>94487080</v>
+        <v>94487531</v>
       </c>
       <c r="B42" t="n">
-        <v>95519</v>
+        <v>78570</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,40 +5336,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462828.0327530226</v>
+        <v>463005.251833215</v>
       </c>
       <c r="R42" t="n">
-        <v>7104731.982492823</v>
+        <v>7104852.450774862</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5440,10 +5437,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>94487531</v>
+        <v>94523110</v>
       </c>
       <c r="B43" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5456,38 +5453,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463005.251833215</v>
+        <v>463077.5864870124</v>
       </c>
       <c r="R43" t="n">
-        <v>7104852.450774862</v>
+        <v>7104816.129870321</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5527,6 +5527,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5541,22 +5546,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>94523110</v>
+        <v>94523117</v>
       </c>
       <c r="B44" t="n">
-        <v>56395</v>
+        <v>96354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5565,42 +5570,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463077.5864870124</v>
+        <v>462985.0853754753</v>
       </c>
       <c r="R44" t="n">
-        <v>7104816.129870321</v>
+        <v>7104852.253069507</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5643,11 +5644,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5674,10 +5670,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>94523117</v>
+        <v>94580773</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
+        <v>56395</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5686,41 +5682,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462985.0853754753</v>
+        <v>462816.9368210531</v>
       </c>
       <c r="R45" t="n">
-        <v>7104852.253069507</v>
+        <v>7104793.844871311</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5760,6 +5760,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5779,17 +5784,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisa Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>94580773</v>
+        <v>94487074</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
+        <v>57290</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5822,21 +5827,25 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462816.9368210531</v>
+        <v>462828</v>
       </c>
       <c r="R46" t="n">
-        <v>7104793.844871311</v>
+        <v>7104732</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5863,24 +5872,14 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5895,19 +5894,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94487074</v>
+        <v>94526736</v>
       </c>
       <c r="B47" t="n">
         <v>57290</v>
@@ -5951,14 +5950,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Valsjöbyn, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462828</v>
+        <v>462821</v>
       </c>
       <c r="R47" t="n">
-        <v>7104732</v>
+        <v>7104784</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6022,10 +6021,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>94526736</v>
+        <v>94486348</v>
       </c>
       <c r="B48" t="n">
-        <v>57290</v>
+        <v>77506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6038,42 +6037,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valsjöbyn, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462821</v>
+        <v>462415.0722872075</v>
       </c>
       <c r="R48" t="n">
-        <v>7104784</v>
+        <v>7104803.055909681</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6103,14 +6095,19 @@
           <t>2021-06-26</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,10 +6134,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>94486348</v>
+        <v>94523112</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6153,38 +6150,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462415.0722872075</v>
+        <v>462410.2086931125</v>
       </c>
       <c r="R49" t="n">
-        <v>7104803.055909681</v>
+        <v>7104799.61235886</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6224,6 +6224,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6238,22 +6243,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>94523112</v>
+        <v>94523139</v>
       </c>
       <c r="B50" t="n">
-        <v>56395</v>
+        <v>89410</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6266,38 +6271,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462410.2086931125</v>
+        <v>462465.1058273449</v>
       </c>
       <c r="R50" t="n">
-        <v>7104799.61235886</v>
+        <v>7104735.468004429</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6340,11 +6341,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6371,10 +6367,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>94523139</v>
+        <v>94486575</v>
       </c>
       <c r="B51" t="n">
-        <v>89410</v>
+        <v>57290</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6387,37 +6383,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462465.1058273449</v>
+        <v>462522</v>
       </c>
       <c r="R51" t="n">
-        <v>7104735.468004429</v>
+        <v>7104725</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6444,19 +6448,14 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6471,22 +6470,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>94486575</v>
+        <v>91847672</v>
       </c>
       <c r="B52" t="n">
-        <v>57290</v>
+        <v>77668</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6495,46 +6494,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462522</v>
+        <v>464900.9499506403</v>
       </c>
       <c r="R52" t="n">
-        <v>7104725</v>
+        <v>7105498.888324833</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6561,17 +6552,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6591,17 +6587,21 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>91847672</v>
+        <v>91847547</v>
       </c>
       <c r="B53" t="n">
-        <v>77668</v>
+        <v>78596</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6610,25 +6610,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464900.9499506403</v>
+        <v>464704.8987313994</v>
       </c>
       <c r="R53" t="n">
-        <v>7105498.888324833</v>
+        <v>7104752.1338409</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6714,7 +6714,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>91847547</v>
+        <v>91847491</v>
       </c>
       <c r="B54" t="n">
         <v>78596</v>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464704.8987313994</v>
+        <v>465121.083554794</v>
       </c>
       <c r="R54" t="n">
-        <v>7104752.1338409</v>
+        <v>7105081.016472445</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>91847491</v>
+        <v>91847571</v>
       </c>
       <c r="B55" t="n">
         <v>78596</v>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465121.083554794</v>
+        <v>464718.9453457455</v>
       </c>
       <c r="R55" t="n">
-        <v>7105081.016472445</v>
+        <v>7104715.199496361</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>91847571</v>
+        <v>91847497</v>
       </c>
       <c r="B56" t="n">
         <v>78596</v>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464718.9453457455</v>
+        <v>465055.0106924323</v>
       </c>
       <c r="R56" t="n">
-        <v>7104715.199496361</v>
+        <v>7105051.991766606</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7062,10 +7062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>91847497</v>
+        <v>91847559</v>
       </c>
       <c r="B57" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7074,25 +7074,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465055.0106924323</v>
+        <v>465174.939870445</v>
       </c>
       <c r="R57" t="n">
-        <v>7105051.991766606</v>
+        <v>7105076.035098969</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>91847559</v>
+        <v>91847647</v>
       </c>
       <c r="B58" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7190,25 +7190,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465174.939870445</v>
+        <v>464930.1128962915</v>
       </c>
       <c r="R58" t="n">
-        <v>7105076.035098969</v>
+        <v>7105520.005714957</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7294,10 +7294,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>91847647</v>
+        <v>91847560</v>
       </c>
       <c r="B59" t="n">
-        <v>78596</v>
+        <v>78603</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464930.1128962915</v>
+        <v>465174.939870445</v>
       </c>
       <c r="R59" t="n">
-        <v>7105520.005714957</v>
+        <v>7105076.035098969</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7410,10 +7410,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>91847560</v>
+        <v>91847580</v>
       </c>
       <c r="B60" t="n">
-        <v>78603</v>
+        <v>85703</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7422,25 +7422,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465174.939870445</v>
+        <v>465000.9615157465</v>
       </c>
       <c r="R60" t="n">
-        <v>7105076.035098969</v>
+        <v>7105000.94494062</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>91847580</v>
+        <v>91847572</v>
       </c>
       <c r="B61" t="n">
-        <v>85703</v>
+        <v>78569</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465000.9615157465</v>
+        <v>464718.9453457455</v>
       </c>
       <c r="R61" t="n">
-        <v>7105000.94494062</v>
+        <v>7104715.199496361</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>91847572</v>
+        <v>91847578</v>
       </c>
       <c r="B62" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464718.9453457455</v>
+        <v>464828.9828857867</v>
       </c>
       <c r="R62" t="n">
-        <v>7104715.199496361</v>
+        <v>7104987.126906457</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>91847578</v>
+        <v>91847658</v>
       </c>
       <c r="B63" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7770,25 +7770,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464828.9828857867</v>
+        <v>464478.0560810776</v>
       </c>
       <c r="R63" t="n">
-        <v>7104987.126906457</v>
+        <v>7105117.190268648</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>91847658</v>
+        <v>91847574</v>
       </c>
       <c r="B64" t="n">
-        <v>78596</v>
+        <v>78602</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7890,21 +7890,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464478.0560810776</v>
+        <v>464718.9453457455</v>
       </c>
       <c r="R64" t="n">
-        <v>7105117.190268648</v>
+        <v>7104715.199496361</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>91847574</v>
+        <v>91847657</v>
       </c>
       <c r="B65" t="n">
-        <v>78602</v>
+        <v>89410</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8002,25 +8002,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464718.9453457455</v>
+        <v>464476.0629247468</v>
       </c>
       <c r="R65" t="n">
-        <v>7104715.199496361</v>
+        <v>7105287.928238258</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8106,10 +8106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>91847657</v>
+        <v>91847662</v>
       </c>
       <c r="B66" t="n">
-        <v>89410</v>
+        <v>89832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8118,25 +8118,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464476.0629247468</v>
+        <v>464232.99871226</v>
       </c>
       <c r="R66" t="n">
-        <v>7105287.928238258</v>
+        <v>7105456.169767317</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>91847662</v>
+        <v>91847648</v>
       </c>
       <c r="B67" t="n">
-        <v>89832</v>
+        <v>78602</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8234,25 +8234,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464232.99871226</v>
+        <v>464930.1128962915</v>
       </c>
       <c r="R67" t="n">
-        <v>7105456.169767317</v>
+        <v>7105520.005714957</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>91847648</v>
+        <v>91847651</v>
       </c>
       <c r="B68" t="n">
-        <v>78602</v>
+        <v>89392</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8350,25 +8350,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8378,10 +8378,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464930.1128962915</v>
+        <v>464304.1140304719</v>
       </c>
       <c r="R68" t="n">
-        <v>7105520.005714957</v>
+        <v>7105428.214786817</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>91847651</v>
+        <v>91847718</v>
       </c>
       <c r="B69" t="n">
-        <v>89392</v>
+        <v>89410</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8470,21 +8470,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464304.1140304719</v>
+        <v>465328.190275298</v>
       </c>
       <c r="R69" t="n">
-        <v>7105428.214786817</v>
+        <v>7105611.827783358</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8570,10 +8570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>91847718</v>
+        <v>91847650</v>
       </c>
       <c r="B70" t="n">
-        <v>89410</v>
+        <v>89356</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8582,25 +8582,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465328.190275298</v>
+        <v>464304.1140304719</v>
       </c>
       <c r="R70" t="n">
-        <v>7105611.827783358</v>
+        <v>7105428.214786817</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>91847650</v>
+        <v>91847573</v>
       </c>
       <c r="B71" t="n">
-        <v>89356</v>
+        <v>78603</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8702,21 +8702,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464304.1140304719</v>
+        <v>464718.9453457455</v>
       </c>
       <c r="R71" t="n">
-        <v>7105428.214786817</v>
+        <v>7104715.199496361</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8802,10 +8802,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>91847573</v>
+        <v>91847639</v>
       </c>
       <c r="B72" t="n">
-        <v>78603</v>
+        <v>78596</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8818,21 +8818,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464718.9453457455</v>
+        <v>465049.8875694345</v>
       </c>
       <c r="R72" t="n">
-        <v>7104715.199496361</v>
+        <v>7105453.878285721</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>91847639</v>
+        <v>91847577</v>
       </c>
       <c r="B73" t="n">
         <v>78596</v>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465049.8875694345</v>
+        <v>464828.9828857867</v>
       </c>
       <c r="R73" t="n">
-        <v>7105453.878285721</v>
+        <v>7104987.126906457</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>91847577</v>
+        <v>91847498</v>
       </c>
       <c r="B74" t="n">
-        <v>78596</v>
+        <v>78602</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9050,21 +9050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464828.9828857867</v>
+        <v>465055.0106924323</v>
       </c>
       <c r="R74" t="n">
-        <v>7104987.126906457</v>
+        <v>7105051.991766606</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>91847498</v>
+        <v>91847661</v>
       </c>
       <c r="B75" t="n">
-        <v>78602</v>
+        <v>78596</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9166,21 +9166,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9190,10 +9190,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465055.0106924323</v>
+        <v>464847.9403836335</v>
       </c>
       <c r="R75" t="n">
-        <v>7105051.991766606</v>
+        <v>7105616.78574343</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>91847661</v>
+        <v>91847666</v>
       </c>
       <c r="B76" t="n">
         <v>78596</v>
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464847.9403836335</v>
+        <v>464877.0560383914</v>
       </c>
       <c r="R76" t="n">
-        <v>7105616.78574343</v>
+        <v>7105595.010527033</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9382,10 +9382,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91847666</v>
+        <v>91847640</v>
       </c>
       <c r="B77" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9394,25 +9394,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9422,10 +9422,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464877.0560383914</v>
+        <v>465049.8875694345</v>
       </c>
       <c r="R77" t="n">
-        <v>7105595.010527033</v>
+        <v>7105453.878285721</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9498,10 +9498,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>91847640</v>
+        <v>91847659</v>
       </c>
       <c r="B78" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9510,25 +9510,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9538,10 +9538,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465049.8875694345</v>
+        <v>464658.9624657584</v>
       </c>
       <c r="R78" t="n">
-        <v>7105453.878285721</v>
+        <v>7105299.849959354</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>91847659</v>
+        <v>91847558</v>
       </c>
       <c r="B79" t="n">
         <v>78596</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464658.9624657584</v>
+        <v>465174.939870445</v>
       </c>
       <c r="R79" t="n">
-        <v>7105299.849959354</v>
+        <v>7105076.035098969</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>91847558</v>
+        <v>91847492</v>
       </c>
       <c r="B80" t="n">
-        <v>78596</v>
+        <v>78603</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465174.939870445</v>
+        <v>465121.083554794</v>
       </c>
       <c r="R80" t="n">
-        <v>7105076.035098969</v>
+        <v>7105081.016472445</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9846,10 +9846,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>91847492</v>
+        <v>91847642</v>
       </c>
       <c r="B81" t="n">
-        <v>78603</v>
+        <v>56395</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9858,25 +9858,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465121.083554794</v>
+        <v>464899.7965107362</v>
       </c>
       <c r="R81" t="n">
-        <v>7105081.016472445</v>
+        <v>7105357.962590555</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9932,6 +9932,11 @@
       <c r="AB81" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9962,10 +9967,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>91847642</v>
+        <v>91847579</v>
       </c>
       <c r="B82" t="n">
-        <v>56395</v>
+        <v>78602</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9974,25 +9979,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10002,10 +10007,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464899.7965107362</v>
+        <v>464828.9828857867</v>
       </c>
       <c r="R82" t="n">
-        <v>7105357.962590555</v>
+        <v>7104987.126906457</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10048,11 +10053,6 @@
       <c r="AB82" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>91847579</v>
+        <v>91847652</v>
       </c>
       <c r="B83" t="n">
-        <v>78602</v>
+        <v>89832</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10095,25 +10095,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464828.9828857867</v>
+        <v>464304.1140304719</v>
       </c>
       <c r="R83" t="n">
-        <v>7104987.126906457</v>
+        <v>7105428.214786817</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10199,10 +10199,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>91847652</v>
+        <v>91847645</v>
       </c>
       <c r="B84" t="n">
-        <v>89832</v>
+        <v>56395</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10211,25 +10211,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10239,10 +10239,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464304.1140304719</v>
+        <v>464930.1128962915</v>
       </c>
       <c r="R84" t="n">
-        <v>7105428.214786817</v>
+        <v>7105520.005714957</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10285,6 +10285,11 @@
       <c r="AB84" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10315,10 +10320,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>91847645</v>
+        <v>91953553</v>
       </c>
       <c r="B85" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10331,21 +10336,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10355,13 +10360,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464930.1128962915</v>
+        <v>464711.9274702939</v>
       </c>
       <c r="R85" t="n">
-        <v>7105520.005714957</v>
+        <v>7104714.841356706</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10401,11 +10406,6 @@
       <c r="AB85" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10436,10 +10436,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>91953553</v>
+        <v>91953582</v>
       </c>
       <c r="B86" t="n">
-        <v>78569</v>
+        <v>77668</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10448,25 +10448,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464711.9274702939</v>
+        <v>464900.9746653602</v>
       </c>
       <c r="R86" t="n">
-        <v>7104714.841356706</v>
+        <v>7105501.076485523</v>
       </c>
       <c r="S86" t="n">
         <v>50</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>91953582</v>
+        <v>91953583</v>
       </c>
       <c r="B87" t="n">
-        <v>77668</v>
+        <v>78570</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10564,25 +10564,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464900.9746653602</v>
+        <v>465049.035775098</v>
       </c>
       <c r="R87" t="n">
-        <v>7105501.076485523</v>
+        <v>7105456.076334454</v>
       </c>
       <c r="S87" t="n">
         <v>50</v>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>91953583</v>
+        <v>94489320</v>
       </c>
       <c r="B88" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10684,37 +10684,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465049.035775098</v>
+        <v>463973.8958438191</v>
       </c>
       <c r="R88" t="n">
-        <v>7105456.076334454</v>
+        <v>7104540.7390351</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10738,7 +10739,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
@@ -10748,7 +10749,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -10773,18 +10774,14 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>94489320</v>
+        <v>94488394</v>
       </c>
       <c r="B89" t="n">
         <v>77506</v>
@@ -10825,10 +10822,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>463973.8958438191</v>
+        <v>463811.218509699</v>
       </c>
       <c r="R89" t="n">
-        <v>7104540.7390351</v>
+        <v>7104763.722965725</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10897,10 +10894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>94488394</v>
+        <v>94490509</v>
       </c>
       <c r="B90" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10913,21 +10910,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10938,10 +10935,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>463811.218509699</v>
+        <v>464057.2253953741</v>
       </c>
       <c r="R90" t="n">
-        <v>7104763.722965725</v>
+        <v>7104657.547404063</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -11010,7 +11007,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>94490509</v>
+        <v>94523137</v>
       </c>
       <c r="B91" t="n">
         <v>89410</v>
@@ -11044,20 +11041,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464057.2253953741</v>
+        <v>463844.5942303116</v>
       </c>
       <c r="R91" t="n">
-        <v>7104657.547404063</v>
+        <v>7104881.974834003</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11111,22 +11107,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>94523137</v>
+        <v>94523143</v>
       </c>
       <c r="B92" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11139,21 +11135,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11163,10 +11159,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>463844.5942303116</v>
+        <v>464002.9074508073</v>
       </c>
       <c r="R92" t="n">
-        <v>7104881.974834003</v>
+        <v>7104698.891933168</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11235,10 +11231,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>94523143</v>
+        <v>94523127</v>
       </c>
       <c r="B93" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11251,21 +11247,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11275,10 +11271,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464002.9074508073</v>
+        <v>463984.0001026748</v>
       </c>
       <c r="R93" t="n">
-        <v>7104698.891933168</v>
+        <v>7104769.596543543</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11347,10 +11343,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>94523127</v>
+        <v>94523134</v>
       </c>
       <c r="B94" t="n">
-        <v>78570</v>
+        <v>89388</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11363,21 +11359,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11387,10 +11383,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>463984.0001026748</v>
+        <v>463867.2061912215</v>
       </c>
       <c r="R94" t="n">
-        <v>7104769.596543543</v>
+        <v>7104904.038522795</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11459,7 +11455,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94523134</v>
+        <v>94523135</v>
       </c>
       <c r="B95" t="n">
         <v>89388</v>
@@ -11499,10 +11495,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>463867.2061912215</v>
+        <v>463888.0157535217</v>
       </c>
       <c r="R95" t="n">
-        <v>7104904.038522795</v>
+        <v>7104846.447591157</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11571,10 +11567,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>94523135</v>
+        <v>94523142</v>
       </c>
       <c r="B96" t="n">
-        <v>89388</v>
+        <v>77506</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11587,21 +11583,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11611,10 +11607,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>463888.0157535217</v>
+        <v>463919.4773213151</v>
       </c>
       <c r="R96" t="n">
-        <v>7104846.447591157</v>
+        <v>7104800.114650953</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11683,10 +11679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>94523142</v>
+        <v>94523128</v>
       </c>
       <c r="B97" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11699,21 +11695,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11723,10 +11719,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>463919.4773213151</v>
+        <v>463872.6525402289</v>
       </c>
       <c r="R97" t="n">
-        <v>7104800.114650953</v>
+        <v>7104731.486945978</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11795,7 +11791,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>94523128</v>
+        <v>94523123</v>
       </c>
       <c r="B98" t="n">
         <v>78570</v>
@@ -11835,10 +11831,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>463872.6525402289</v>
+        <v>463937.1767083969</v>
       </c>
       <c r="R98" t="n">
-        <v>7104731.486945978</v>
+        <v>7104814.356286853</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11907,10 +11903,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>94523123</v>
+        <v>94523145</v>
       </c>
       <c r="B99" t="n">
-        <v>78570</v>
+        <v>89406</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11923,21 +11919,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11947,10 +11943,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>463937.1767083969</v>
+        <v>463831.4864733052</v>
       </c>
       <c r="R99" t="n">
-        <v>7104814.356286853</v>
+        <v>7104885.629555423</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12001,6 +11997,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12019,10 +12016,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>94523145</v>
+        <v>94523138</v>
       </c>
       <c r="B100" t="n">
-        <v>89406</v>
+        <v>89410</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12035,21 +12032,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12059,10 +12056,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>463831.4864733052</v>
+        <v>463691.62764589</v>
       </c>
       <c r="R100" t="n">
-        <v>7104885.629555423</v>
+        <v>7104733.158305655</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12113,7 +12110,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12132,10 +12128,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>94523138</v>
+        <v>94523141</v>
       </c>
       <c r="B101" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12148,21 +12144,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12172,10 +12168,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>463691.62764589</v>
+        <v>463942.8443011101</v>
       </c>
       <c r="R101" t="n">
-        <v>7104733.158305655</v>
+        <v>7104925.048862137</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12244,10 +12240,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>94523141</v>
+        <v>94523125</v>
       </c>
       <c r="B102" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12260,21 +12256,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12284,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>463942.8443011101</v>
+        <v>463955.5545582641</v>
       </c>
       <c r="R102" t="n">
-        <v>7104925.048862137</v>
+        <v>7104811.516399338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12356,10 +12352,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>94523125</v>
+        <v>94523130</v>
       </c>
       <c r="B103" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12372,21 +12368,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12396,10 +12392,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>463955.5545582641</v>
+        <v>463883.783996609</v>
       </c>
       <c r="R103" t="n">
-        <v>7104811.516399338</v>
+        <v>7104708.591934055</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12468,10 +12464,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>94523130</v>
+        <v>94523116</v>
       </c>
       <c r="B104" t="n">
-        <v>78569</v>
+        <v>96354</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12480,25 +12476,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12508,10 +12504,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>463883.783996609</v>
+        <v>463869.1017777031</v>
       </c>
       <c r="R104" t="n">
-        <v>7104708.591934055</v>
+        <v>7104916.27417447</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12580,7 +12576,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>94523116</v>
+        <v>94580775</v>
       </c>
       <c r="B105" t="n">
         <v>96354</v>
@@ -12616,17 +12612,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>463869.1017777031</v>
+        <v>464050.7903082664</v>
       </c>
       <c r="R105" t="n">
-        <v>7104916.27417447</v>
+        <v>7104631.790958654</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12685,17 +12681,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lisa Johansson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>94580775</v>
+        <v>94580778</v>
       </c>
       <c r="B106" t="n">
-        <v>96354</v>
+        <v>77668</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12704,25 +12700,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>1249</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12732,10 +12728,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464050.7903082664</v>
+        <v>464375.3823567145</v>
       </c>
       <c r="R106" t="n">
-        <v>7104631.790958654</v>
+        <v>7104954.645085484</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12804,10 +12800,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>94580778</v>
+        <v>94580779</v>
       </c>
       <c r="B107" t="n">
-        <v>77668</v>
+        <v>96237</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12816,25 +12812,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1249</v>
+        <v>220093</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12844,10 +12840,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464375.3823567145</v>
+        <v>464563.1710386831</v>
       </c>
       <c r="R107" t="n">
-        <v>7104954.645085484</v>
+        <v>7104663.121644213</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12916,10 +12912,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>94580779</v>
+        <v>94444807</v>
       </c>
       <c r="B108" t="n">
-        <v>96237</v>
+        <v>56411</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12928,41 +12924,49 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Valsjön 1:212 spillkråka, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464563.1710386831</v>
+        <v>462274.151300853</v>
       </c>
       <c r="R108" t="n">
-        <v>7104663.121644213</v>
+        <v>7104569.220266674</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12986,22 +12990,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Otroligt välarbetad gran. Stora hackhål efter hästmyra troligen.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13016,22 +13025,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>94444807</v>
+        <v>94523111</v>
       </c>
       <c r="B109" t="n">
-        <v>56411</v>
+        <v>56395</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13044,16 +13053,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -13064,25 +13073,21 @@
       <c r="I109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Valsjön 1:212 spillkråka, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462274.151300853</v>
+        <v>462679.8678831077</v>
       </c>
       <c r="R109" t="n">
-        <v>7104569.220266674</v>
+        <v>7104586.214458161</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13106,27 +13111,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Otroligt välarbetad gran. Stora hackhål efter hästmyra troligen.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13141,22 +13146,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>94523111</v>
+        <v>91847686</v>
       </c>
       <c r="B110" t="n">
-        <v>56395</v>
+        <v>78527</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13165,45 +13170,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462679.8678831077</v>
+        <v>461919.9781842643</v>
       </c>
       <c r="R110" t="n">
-        <v>7104586.214458161</v>
+        <v>7104465.830702319</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13227,7 +13228,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
@@ -13237,17 +13238,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13262,22 +13258,26 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>91847686</v>
+        <v>91847712</v>
       </c>
       <c r="B111" t="n">
-        <v>78527</v>
+        <v>78570</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13286,25 +13286,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13314,10 +13314,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461919.9781842643</v>
+        <v>461936.0199903366</v>
       </c>
       <c r="R111" t="n">
-        <v>7104465.830702319</v>
+        <v>7104451.185356237</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13390,10 +13390,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>91847712</v>
+        <v>94451806</v>
       </c>
       <c r="B112" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13406,37 +13406,40 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Valsjöbyn, Torshöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461936.0199903366</v>
+        <v>462029.970096346</v>
       </c>
       <c r="R112" t="n">
-        <v>7104451.185356237</v>
+        <v>7104425.954852367</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13460,7 +13463,7 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -13470,7 +13473,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
@@ -13484,32 +13487,29 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Adolfsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Magnus Adolfsson, Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>94451806</v>
+        <v>94451832</v>
       </c>
       <c r="B113" t="n">
-        <v>73698</v>
+        <v>81236</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13522,21 +13522,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462029.970096346</v>
+        <v>462014.066523139</v>
       </c>
       <c r="R113" t="n">
-        <v>7104425.954852367</v>
+        <v>7104416.078575912</v>
       </c>
       <c r="S113" t="n">
         <v>100</v>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>94451832</v>
+        <v>94451412</v>
       </c>
       <c r="B114" t="n">
-        <v>81236</v>
+        <v>78570</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13638,21 +13638,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13665,10 +13665,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462014.066523139</v>
+        <v>462013.3886219114</v>
       </c>
       <c r="R114" t="n">
-        <v>7104416.078575912</v>
+        <v>7104539.996190672</v>
       </c>
       <c r="S114" t="n">
         <v>100</v>
@@ -13738,10 +13738,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>94451412</v>
+        <v>94450504</v>
       </c>
       <c r="B115" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13754,26 +13754,30 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13781,13 +13785,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462013.3886219114</v>
+        <v>462026.5923819891</v>
       </c>
       <c r="R115" t="n">
-        <v>7104539.996190672</v>
+        <v>7104616.016965177</v>
       </c>
       <c r="S115" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13854,10 +13858,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>94450504</v>
+        <v>94450274</v>
       </c>
       <c r="B116" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13870,30 +13874,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462026.5923819891</v>
+        <v>461902.6107770037</v>
       </c>
       <c r="R116" t="n">
-        <v>7104616.016965177</v>
+        <v>7104479.616626331</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>94450274</v>
+        <v>94523120</v>
       </c>
       <c r="B117" t="n">
         <v>78570</v>
@@ -14008,22 +14008,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Valsjöbyn, Torshöjden, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461902.6107770037</v>
+        <v>461930.5144966884</v>
       </c>
       <c r="R117" t="n">
-        <v>7104479.616626331</v>
+        <v>7104467.015193742</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14047,7 +14044,7 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
@@ -14057,7 +14054,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -14071,26 +14068,25 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Magnus Adolfsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Magnus Adolfsson, Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>94523120</v>
+        <v>94523121</v>
       </c>
       <c r="B118" t="n">
         <v>78570</v>
@@ -14130,10 +14126,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461930.5144966884</v>
+        <v>461961.4975639902</v>
       </c>
       <c r="R118" t="n">
-        <v>7104467.015193742</v>
+        <v>7104455.251979004</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14202,7 +14198,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>94523121</v>
+        <v>94523119</v>
       </c>
       <c r="B119" t="n">
         <v>78570</v>
@@ -14242,10 +14238,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461961.4975639902</v>
+        <v>461925.2396096346</v>
       </c>
       <c r="R119" t="n">
-        <v>7104455.251979004</v>
+        <v>7104501.669279547</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14314,7 +14310,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>94523119</v>
+        <v>91847682</v>
       </c>
       <c r="B120" t="n">
         <v>78570</v>
@@ -14350,17 +14346,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461925.2396096346</v>
+        <v>462319.7965785815</v>
       </c>
       <c r="R120" t="n">
-        <v>7104501.669279547</v>
+        <v>7104211.816218408</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14384,7 +14380,7 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
@@ -14394,7 +14390,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -14414,22 +14410,26 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>91847682</v>
+        <v>94444787</v>
       </c>
       <c r="B121" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14442,37 +14442,45 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Valsjön 1:212 ringhack, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462319.7965785815</v>
+        <v>462260.2384020471</v>
       </c>
       <c r="R121" t="n">
-        <v>7104211.816218408</v>
+        <v>7104325.94705083</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14496,22 +14504,27 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Färska ringhack i välbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14526,26 +14539,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>94444787</v>
+        <v>94492697</v>
       </c>
       <c r="B122" t="n">
-        <v>56395</v>
+        <v>96254</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14554,49 +14563,39 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Valsjön 1:212 ringhack, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462260.2384020471</v>
+        <v>462257.562952688</v>
       </c>
       <c r="R122" t="n">
-        <v>7104325.94705083</v>
+        <v>7104286.133779494</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14620,27 +14619,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Färska ringhack i välbearbetad död gran.</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14655,22 +14649,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>94492697</v>
+        <v>94523122</v>
       </c>
       <c r="B123" t="n">
-        <v>96254</v>
+        <v>78570</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14679,39 +14673,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>223597</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462257.562952688</v>
+        <v>462331.5941276685</v>
       </c>
       <c r="R123" t="n">
-        <v>7104286.133779494</v>
+        <v>7104280.857276356</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14765,22 +14761,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>94523122</v>
+        <v>91847584</v>
       </c>
       <c r="B124" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14789,41 +14785,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462331.5941276685</v>
+        <v>464447.8257088873</v>
       </c>
       <c r="R124" t="n">
-        <v>7104280.857276356</v>
+        <v>7104160.044302321</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14847,7 +14843,7 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
@@ -14857,7 +14853,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -14877,22 +14873,26 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>91847584</v>
+        <v>91847585</v>
       </c>
       <c r="B125" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14901,25 +14901,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15005,10 +15005,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>91847585</v>
+        <v>91847627</v>
       </c>
       <c r="B126" t="n">
-        <v>78570</v>
+        <v>89356</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15017,25 +15017,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15045,10 +15045,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464447.8257088873</v>
+        <v>464389.8314009494</v>
       </c>
       <c r="R126" t="n">
-        <v>7104160.044302321</v>
+        <v>7104187.856287077</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -15121,10 +15121,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>91847627</v>
+        <v>91847628</v>
       </c>
       <c r="B127" t="n">
-        <v>89356</v>
+        <v>89410</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15133,25 +15133,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15161,10 +15161,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464389.8314009494</v>
+        <v>464434.0578151146</v>
       </c>
       <c r="R127" t="n">
-        <v>7104187.856287077</v>
+        <v>7104182.971323023</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -15237,10 +15237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>91847628</v>
+        <v>91953585</v>
       </c>
       <c r="B128" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15253,21 +15253,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15277,13 +15277,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464434.0578151146</v>
+        <v>463757.9931134701</v>
       </c>
       <c r="R128" t="n">
-        <v>7104182.971323023</v>
+        <v>7104259.086236862</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15323,6 +15323,11 @@
       <c r="AB128" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15353,10 +15358,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>91953585</v>
+        <v>94489922</v>
       </c>
       <c r="B129" t="n">
-        <v>77506</v>
+        <v>96354</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15365,41 +15370,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>463757.9931134701</v>
+        <v>464227.6499595161</v>
       </c>
       <c r="R129" t="n">
-        <v>7104259.086236862</v>
+        <v>7104381.938951407</v>
       </c>
       <c r="S129" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15423,7 +15430,7 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
@@ -15433,17 +15440,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15463,21 +15465,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>94489922</v>
+        <v>94489368</v>
       </c>
       <c r="B130" t="n">
-        <v>96354</v>
+        <v>77506</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15486,40 +15484,39 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464227.6499595161</v>
+        <v>464027.7552437605</v>
       </c>
       <c r="R130" t="n">
-        <v>7104381.938951407</v>
+        <v>7104459.554336783</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15588,7 +15585,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>94489368</v>
+        <v>94523140</v>
       </c>
       <c r="B131" t="n">
         <v>77506</v>
@@ -15622,20 +15619,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>464027.7552437605</v>
+        <v>463815.4605240455</v>
       </c>
       <c r="R131" t="n">
-        <v>7104459.554336783</v>
+        <v>7104261.91981072</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15689,22 +15685,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>94523140</v>
+        <v>91847710</v>
       </c>
       <c r="B132" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15717,37 +15713,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>463815.4605240455</v>
+        <v>462973.1785877153</v>
       </c>
       <c r="R132" t="n">
-        <v>7104261.91981072</v>
+        <v>7104294.167822956</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15771,7 +15767,7 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
@@ -15781,7 +15777,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -15801,22 +15797,26 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>91847710</v>
+        <v>91847680</v>
       </c>
       <c r="B133" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15829,21 +15829,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15853,10 +15853,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462973.1785877153</v>
+        <v>462538.9032046349</v>
       </c>
       <c r="R133" t="n">
-        <v>7104294.167822956</v>
+        <v>7104093.128753767</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15929,10 +15929,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>91847680</v>
+        <v>91847674</v>
       </c>
       <c r="B134" t="n">
-        <v>73698</v>
+        <v>56395</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15945,21 +15945,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15969,10 +15969,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462538.9032046349</v>
+        <v>462413.8203972606</v>
       </c>
       <c r="R134" t="n">
-        <v>7104093.128753767</v>
+        <v>7104191.849335553</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -16015,6 +16015,11 @@
       <c r="AB134" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16045,10 +16050,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>91847674</v>
+        <v>91847708</v>
       </c>
       <c r="B135" t="n">
-        <v>56395</v>
+        <v>78596</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16057,25 +16062,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16085,10 +16090,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462413.8203972606</v>
+        <v>462973.1785877153</v>
       </c>
       <c r="R135" t="n">
-        <v>7104191.849335553</v>
+        <v>7104294.167822956</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -16131,11 +16136,6 @@
       <c r="AB135" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16166,10 +16166,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>91847708</v>
+        <v>91847711</v>
       </c>
       <c r="B136" t="n">
-        <v>78596</v>
+        <v>78602</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16282,10 +16282,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>91847711</v>
+        <v>91953586</v>
       </c>
       <c r="B137" t="n">
-        <v>78602</v>
+        <v>77506</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16294,20 +16294,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -16322,13 +16322,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>462973.1785877153</v>
+        <v>462773.0096326948</v>
       </c>
       <c r="R137" t="n">
-        <v>7104294.167822956</v>
+        <v>7104053.971643656</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16368,6 +16368,11 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16398,10 +16403,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>91953586</v>
+        <v>94452148</v>
       </c>
       <c r="B138" t="n">
-        <v>77506</v>
+        <v>89952</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16410,41 +16415,44 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Valsjöbyn, Torshöjden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462773.0096326948</v>
+        <v>462351.2077399952</v>
       </c>
       <c r="R138" t="n">
-        <v>7104053.971643656</v>
+        <v>7104235.081040238</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16468,7 +16476,7 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
@@ -16478,7 +16486,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
@@ -16486,43 +16494,35 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Adolfsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Magnus Adolfsson, Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>94452148</v>
+        <v>94492300</v>
       </c>
       <c r="B139" t="n">
-        <v>89952</v>
+        <v>78570</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16531,44 +16531,42 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Valsjöbyn, Torshöjden, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462351.2077399952</v>
+        <v>462565.9782844005</v>
       </c>
       <c r="R139" t="n">
-        <v>7104235.081040238</v>
+        <v>7104084.044773481</v>
       </c>
       <c r="S139" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16592,7 +16590,7 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
@@ -16602,7 +16600,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
@@ -16616,29 +16614,28 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Magnus Adolfsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Magnus Adolfsson, Kristofer Holmsten</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>94492300</v>
+        <v>94492378</v>
       </c>
       <c r="B140" t="n">
-        <v>78570</v>
+        <v>89410</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16651,21 +16648,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16676,10 +16673,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>462565.9782844005</v>
+        <v>462547.4021449768</v>
       </c>
       <c r="R140" t="n">
-        <v>7104084.044773481</v>
+        <v>7104070.693685829</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16748,10 +16745,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>94492378</v>
+        <v>94523109</v>
       </c>
       <c r="B141" t="n">
-        <v>89410</v>
+        <v>56395</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16764,38 +16761,41 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462547.4021449768</v>
+        <v>462423.8026341717</v>
       </c>
       <c r="R141" t="n">
-        <v>7104070.693685829</v>
+        <v>7104183.408932171</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16835,6 +16835,11 @@
       <c r="AB141" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16849,22 +16854,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>94523109</v>
+        <v>94523115</v>
       </c>
       <c r="B142" t="n">
-        <v>56395</v>
+        <v>96354</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16873,42 +16878,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462423.8026341717</v>
+        <v>462800.7267972961</v>
       </c>
       <c r="R142" t="n">
-        <v>7104183.408932171</v>
+        <v>7104025.176370968</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16951,11 +16952,6 @@
       <c r="AB142" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16982,10 +16978,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>94523115</v>
+        <v>94492384</v>
       </c>
       <c r="B143" t="n">
-        <v>96354</v>
+        <v>57290</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16994,41 +16990,49 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462800.7267972961</v>
+        <v>462547</v>
       </c>
       <c r="R143" t="n">
-        <v>7104025.176370968</v>
+        <v>7104071</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17055,19 +17059,14 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17082,22 +17081,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>94492384</v>
+        <v>91847707</v>
       </c>
       <c r="B144" t="n">
-        <v>57290</v>
+        <v>89406</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17110,42 +17109,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462547</v>
+        <v>463199.217340311</v>
       </c>
       <c r="R144" t="n">
-        <v>7104071</v>
+        <v>7104315.128621005</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -17172,17 +17163,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17202,17 +17198,21 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>91847707</v>
+        <v>91847678</v>
       </c>
       <c r="B145" t="n">
-        <v>89406</v>
+        <v>89410</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17225,21 +17225,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>463199.217340311</v>
+        <v>463168.0987098275</v>
       </c>
       <c r="R145" t="n">
-        <v>7104315.128621005</v>
+        <v>7104315.934981376</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17325,10 +17325,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>91847678</v>
+        <v>91847701</v>
       </c>
       <c r="B146" t="n">
-        <v>89410</v>
+        <v>78569</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17341,21 +17341,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17365,10 +17365,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>463168.0987098275</v>
+        <v>463185.1984299953</v>
       </c>
       <c r="R146" t="n">
-        <v>7104315.934981376</v>
+        <v>7104204.951772586</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17441,10 +17441,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>91847701</v>
+        <v>91847706</v>
       </c>
       <c r="B147" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17457,21 +17457,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17481,10 +17481,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>463185.1984299953</v>
+        <v>463049.1253165146</v>
       </c>
       <c r="R147" t="n">
-        <v>7104204.951772586</v>
+        <v>7104154.896121416</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17557,10 +17557,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>91847706</v>
+        <v>91847700</v>
       </c>
       <c r="B148" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17573,21 +17573,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17597,10 +17597,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>463049.1253165146</v>
+        <v>463185.1984299953</v>
       </c>
       <c r="R148" t="n">
-        <v>7104154.896121416</v>
+        <v>7104204.951772586</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17673,7 +17673,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>91847700</v>
+        <v>94491641</v>
       </c>
       <c r="B149" t="n">
         <v>78570</v>
@@ -17707,16 +17707,17 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>463185.1984299953</v>
+        <v>463249.0997976987</v>
       </c>
       <c r="R149" t="n">
-        <v>7104204.951772586</v>
+        <v>7104232.657595132</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17743,7 +17744,7 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
@@ -17753,7 +17754,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
@@ -17778,21 +17779,17 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>94491641</v>
+        <v>94580772</v>
       </c>
       <c r="B150" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17805,38 +17802,41 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>463249.0997976987</v>
+        <v>463216.4042791632</v>
       </c>
       <c r="R150" t="n">
-        <v>7104232.657595132</v>
+        <v>7104767.202339236</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17876,6 +17876,11 @@
       <c r="AB150" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17890,22 +17895,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lisa Johansson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>94580772</v>
+        <v>91847681</v>
       </c>
       <c r="B151" t="n">
-        <v>56395</v>
+        <v>73698</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17918,41 +17923,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>463216.4042791632</v>
+        <v>463558.7915540517</v>
       </c>
       <c r="R151" t="n">
-        <v>7104767.202339236</v>
+        <v>7104358.181721956</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17976,7 +17977,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
@@ -17986,17 +17987,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18011,22 +18007,26 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>91847681</v>
+        <v>91847697</v>
       </c>
       <c r="B152" t="n">
-        <v>73698</v>
+        <v>78603</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18035,25 +18035,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1467</v>
+        <v>6464</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18063,10 +18063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>463558.7915540517</v>
+        <v>463572.1344132798</v>
       </c>
       <c r="R152" t="n">
-        <v>7104358.181721956</v>
+        <v>7104337.008332871</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -18139,10 +18139,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>91847697</v>
+        <v>91847671</v>
       </c>
       <c r="B153" t="n">
-        <v>78603</v>
+        <v>73698</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18151,25 +18151,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18179,10 +18179,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>463572.1344132798</v>
+        <v>463488.1813111514</v>
       </c>
       <c r="R153" t="n">
-        <v>7104337.008332871</v>
+        <v>7104915.909849492</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -18255,10 +18255,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>91847671</v>
+        <v>91847696</v>
       </c>
       <c r="B154" t="n">
-        <v>73698</v>
+        <v>78569</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18271,21 +18271,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18295,10 +18295,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>463488.1813111514</v>
+        <v>463572.1344132798</v>
       </c>
       <c r="R154" t="n">
-        <v>7104915.909849492</v>
+        <v>7104337.008332871</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18371,7 +18371,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>91847696</v>
+        <v>91847684</v>
       </c>
       <c r="B155" t="n">
         <v>78569</v>
@@ -18411,10 +18411,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>463572.1344132798</v>
+        <v>463563.9880350386</v>
       </c>
       <c r="R155" t="n">
-        <v>7104337.008332871</v>
+        <v>7104390.083933746</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18487,10 +18487,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>91847684</v>
+        <v>91847683</v>
       </c>
       <c r="B156" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18499,25 +18499,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18603,10 +18603,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>91847683</v>
+        <v>91953592</v>
       </c>
       <c r="B157" t="n">
-        <v>78596</v>
+        <v>77506</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18615,25 +18615,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>463563.9880350386</v>
+        <v>463570.0246900913</v>
       </c>
       <c r="R157" t="n">
-        <v>7104390.083933746</v>
+        <v>7104344.038742815</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18689,6 +18689,11 @@
       <c r="AB157" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18712,243 +18717,6 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>91953588</v>
-      </c>
-      <c r="B158" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Jämtlands län, Jmt</t>
-        </is>
-      </c>
-      <c r="Q158" t="n">
-        <v>463564.8544795571</v>
-      </c>
-      <c r="R158" t="n">
-        <v>7104389.198081851</v>
-      </c>
-      <c r="S158" t="n">
-        <v>50</v>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT158" t="inlineStr"/>
-      <c r="AW158" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX158" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>91953592</v>
-      </c>
-      <c r="B159" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Jämtlands län, Jmt</t>
-        </is>
-      </c>
-      <c r="Q159" t="n">
-        <v>463570.0246900913</v>
-      </c>
-      <c r="R159" t="n">
-        <v>7104344.038742815</v>
-      </c>
-      <c r="S159" t="n">
-        <v>50</v>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
-        </is>
-      </c>
-      <c r="AD159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT159" t="inlineStr"/>
-      <c r="AW159" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX159" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
